--- a/data/trans_orig/P05A02-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P05A02-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2007</t>
+          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2007 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>361163</t>
+          <t>363388</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>396826</t>
+          <t>398607</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>217716</t>
+          <t>215258</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>247402</t>
+          <t>246642</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>587607</t>
+          <t>587487</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>635648</t>
+          <t>636156</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,68%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67582</t>
+          <t>66427</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101726</t>
+          <t>100484</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44640</t>
+          <t>44759</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71780</t>
+          <t>72213</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118641</t>
+          <t>117260</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>165320</t>
+          <t>162623</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,88%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16227</t>
+          <t>17409</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10798</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26787</t>
+          <t>26311</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17860</t>
+          <t>17019</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37032</t>
+          <t>36747</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>266342</t>
+          <t>264225</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>298215</t>
+          <t>296787</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>274631</t>
+          <t>274948</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>305749</t>
+          <t>304375</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>550393</t>
+          <t>548855</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>595610</t>
+          <t>593202</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,71%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55420</t>
+          <t>56950</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>86224</t>
+          <t>86467</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48979</t>
+          <t>49999</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>79389</t>
+          <t>79175</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>113805</t>
+          <t>113492</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>155154</t>
+          <t>159289</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,67%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7542</t>
+          <t>7348</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23200</t>
+          <t>21853</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9456</t>
+          <t>9432</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26640</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19974</t>
+          <t>20758</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42378</t>
+          <t>44263</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>404587</t>
+          <t>403841</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>442706</t>
+          <t>445273</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>111061</t>
+          <t>111235</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>133841</t>
+          <t>133356</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>525299</t>
+          <t>526194</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>570201</t>
+          <t>571118</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,52%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78741</t>
+          <t>77336</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>113865</t>
+          <t>113345</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25559</t>
+          <t>25407</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47133</t>
+          <t>45671</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108971</t>
+          <t>107784</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>151364</t>
+          <t>150312</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13120</t>
+          <t>13360</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32767</t>
+          <t>32522</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4226</t>
+          <t>4195</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16672</t>
+          <t>16468</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21375</t>
+          <t>20851</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45489</t>
+          <t>44496</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>907324</t>
+          <t>907884</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>963295</t>
+          <t>965469</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,82 +2116,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>73,42%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>78,08%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>530498</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>505094</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>552601</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>74,47%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>70,9%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>77,57%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1439</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1468490</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>1430033</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>1505107</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>75,35%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>73,38%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>77,9%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>513</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>530498</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>508033</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>553909</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>74,47%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>71,32%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>77,76%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1439</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1468490</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>1430277</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1504960</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>75,35%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>73,39%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,23%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>239175</t>
+          <t>236433</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>293626</t>
+          <t>292540</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>126118</t>
+          <t>127942</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>169815</t>
+          <t>170742</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>376016</t>
+          <t>376243</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>448208</t>
+          <t>447395</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23401</t>
+          <t>24984</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47200</t>
+          <t>48507</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25871</t>
+          <t>24261</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48698</t>
+          <t>47493</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>54021</t>
+          <t>55927</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>87154</t>
+          <t>88742</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257186</t>
+          <t>257938</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287674</t>
+          <t>288919</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>388763</t>
+          <t>390259</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>433984</t>
+          <t>433438</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>657233</t>
+          <t>659426</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>710415</t>
+          <t>714111</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,93%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>53550</t>
+          <t>52989</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>83809</t>
+          <t>83338</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>105767</t>
+          <t>106991</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>148356</t>
+          <t>146716</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>169380</t>
+          <t>169367</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>219358</t>
+          <t>218669</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4241</t>
+          <t>4337</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14956</t>
+          <t>15423</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20275</t>
+          <t>20351</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42165</t>
+          <t>43240</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27907</t>
+          <t>25831</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53865</t>
+          <t>50439</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>242050</t>
+          <t>243360</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>265106</t>
+          <t>266362</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>885071</t>
+          <t>884908</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>949985</t>
+          <t>948105</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1138462</t>
+          <t>1139118</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1203609</t>
+          <t>1207076</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>78,12%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26064</t>
+          <t>24466</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46913</t>
+          <t>45327</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>221085</t>
+          <t>223888</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>277089</t>
+          <t>278956</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>256725</t>
+          <t>252013</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>316077</t>
+          <t>313385</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14776</t>
+          <t>15356</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>64769</t>
+          <t>63606</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>98153</t>
+          <t>98793</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>71118</t>
+          <t>71047</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>108402</t>
+          <t>109821</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2510656</t>
+          <t>2509524</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2601610</t>
+          <t>2600413</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2455728</t>
+          <t>2455804</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2554934</t>
+          <t>2561670</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4988761</t>
+          <t>4996130</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5124014</t>
+          <t>5132656</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,38%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>563439</t>
+          <t>568943</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>651608</t>
+          <t>654484</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>630284</t>
+          <t>627226</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>725203</t>
+          <t>722642</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1232511</t>
+          <t>1224610</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1356802</t>
+          <t>1355178</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>76169</t>
+          <t>76806</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>114697</t>
+          <t>115607</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>163643</t>
+          <t>160339</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>217019</t>
+          <t>215160</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>251582</t>
+          <t>250513</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>315677</t>
+          <t>313737</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2012</t>
+          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2012 (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>358909</t>
+          <t>358181</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>387714</t>
+          <t>388201</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>244545</t>
+          <t>246347</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>272337</t>
+          <t>273642</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>612409</t>
+          <t>609304</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>654871</t>
+          <t>653875</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,22%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33897</t>
+          <t>33175</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61026</t>
+          <t>60052</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32597</t>
+          <t>30680</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58119</t>
+          <t>57130</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>71887</t>
+          <t>72457</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110539</t>
+          <t>111106</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9367</t>
+          <t>9676</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25246</t>
+          <t>26039</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>4795</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15266</t>
+          <t>17090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17227</t>
+          <t>17431</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38037</t>
+          <t>38038</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>324418</t>
+          <t>323371</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>359094</t>
+          <t>359100</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>267398</t>
+          <t>266191</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>295557</t>
+          <t>295756</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>602826</t>
+          <t>602307</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>645246</t>
+          <t>645996</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,99%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49881</t>
+          <t>50739</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83783</t>
+          <t>83775</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31658</t>
+          <t>31204</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57645</t>
+          <t>59491</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>91269</t>
+          <t>89303</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>129906</t>
+          <t>133447</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15906</t>
+          <t>15972</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3493</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16851</t>
+          <t>16229</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9561</t>
+          <t>9661</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26925</t>
+          <t>27422</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>516345</t>
+          <t>519418</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>554463</t>
+          <t>554320</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>205652</t>
+          <t>206520</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>229121</t>
+          <t>230281</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>733304</t>
+          <t>732007</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>777296</t>
+          <t>775117</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,39%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60176</t>
+          <t>60048</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95581</t>
+          <t>93940</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21809</t>
+          <t>21545</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44193</t>
+          <t>43405</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87687</t>
+          <t>88382</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130483</t>
+          <t>131320</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8984</t>
+          <t>8902</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25238</t>
+          <t>24516</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17160</t>
+          <t>15991</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15413</t>
+          <t>15463</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33606</t>
+          <t>35963</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>953040</t>
+          <t>950681</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1001576</t>
+          <t>1001012</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>600875</t>
+          <t>599376</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>645794</t>
+          <t>646174</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1568432</t>
+          <t>1569005</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1635850</t>
+          <t>1635672</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,34%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>117374</t>
+          <t>114922</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>162329</t>
+          <t>161977</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87549</t>
+          <t>87697</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>128343</t>
+          <t>129096</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>214338</t>
+          <t>215264</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>276326</t>
+          <t>275545</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24795</t>
+          <t>25494</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50224</t>
+          <t>50145</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22670</t>
+          <t>21737</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47166</t>
+          <t>47504</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>54108</t>
+          <t>54354</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>89704</t>
+          <t>88923</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>415088</t>
+          <t>414011</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>448517</t>
+          <t>448543</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>613698</t>
+          <t>611999</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>654976</t>
+          <t>653607</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1040045</t>
+          <t>1036532</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1092405</t>
+          <t>1092923</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,98%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>54837</t>
+          <t>55604</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>87033</t>
+          <t>88592</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>79622</t>
+          <t>80508</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>118526</t>
+          <t>115610</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>145144</t>
+          <t>144610</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>196218</t>
+          <t>198332</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>16120</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18185</t>
+          <t>19056</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41948</t>
+          <t>41772</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>25746</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50633</t>
+          <t>52083</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>214854</t>
+          <t>214394</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>237397</t>
+          <t>238087</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>898974</t>
+          <t>899633</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>949012</t>
+          <t>949390</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1122619</t>
+          <t>1124789</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1179478</t>
+          <t>1179843</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,86%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27706</t>
+          <t>27639</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50610</t>
+          <t>50578</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>124354</t>
+          <t>125736</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>169379</t>
+          <t>169186</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>159848</t>
+          <t>160675</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>211901</t>
+          <t>210639</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>24491</t>
+          <t>23880</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>48746</t>
+          <t>49060</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>25133</t>
+          <t>25932</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>51175</t>
+          <t>51881</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2846517</t>
+          <t>2852244</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2929883</t>
+          <t>2939819</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2898215</t>
+          <t>2897978</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2989735</t>
+          <t>2992114</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5775836</t>
+          <t>5776324</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5904222</t>
+          <t>5902151</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,93%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>396228</t>
+          <t>388932</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>477088</t>
+          <t>473432</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>428303</t>
+          <t>427725</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>511164</t>
+          <t>513465</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>844258</t>
+          <t>845136</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>961060</t>
+          <t>960511</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>70034</t>
+          <t>67767</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>107175</t>
+          <t>105566</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>101987</t>
+          <t>100941</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>147093</t>
+          <t>146910</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>182241</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>243744</t>
+          <t>240191</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2016</t>
+          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2016 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>361633</t>
+          <t>362739</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>390165</t>
+          <t>390306</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>278516</t>
+          <t>278947</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>305550</t>
+          <t>305255</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>651967</t>
+          <t>652000</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>690584</t>
+          <t>688027</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,01%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32050</t>
+          <t>31276</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57554</t>
+          <t>57389</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27962</t>
+          <t>28141</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52127</t>
+          <t>51502</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>64798</t>
+          <t>65490</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99821</t>
+          <t>99170</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13750</t>
+          <t>14331</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7286</t>
+          <t>7114</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22368</t>
+          <t>21988</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12077</t>
+          <t>12374</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31247</t>
+          <t>31373</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>317673</t>
+          <t>317799</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>342355</t>
+          <t>342553</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>309633</t>
+          <t>310244</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>335284</t>
+          <t>335500</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>634441</t>
+          <t>637520</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>670830</t>
+          <t>672491</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,67%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24938</t>
+          <t>24021</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47502</t>
+          <t>46829</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29244</t>
+          <t>27663</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>53633</t>
+          <t>52492</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>58695</t>
+          <t>57185</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>92506</t>
+          <t>90701</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3898</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16644</t>
+          <t>16497</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11575</t>
+          <t>11841</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22558</t>
+          <t>22073</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>440350</t>
+          <t>440267</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>470357</t>
+          <t>470455</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>145625</t>
+          <t>145563</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>159563</t>
+          <t>159384</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>592138</t>
+          <t>591645</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>625620</t>
+          <t>625931</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,97%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38147</t>
+          <t>37594</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64567</t>
+          <t>63779</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17547</t>
+          <t>18218</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44732</t>
+          <t>46106</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75459</t>
+          <t>76388</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8999</t>
+          <t>9043</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25332</t>
+          <t>25660</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8476</t>
+          <t>7997</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>10730</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28823</t>
+          <t>27377</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>962216</t>
+          <t>960946</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1011298</t>
+          <t>1010416</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>684340</t>
+          <t>687227</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>724944</t>
+          <t>726639</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1663808</t>
+          <t>1662571</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1726211</t>
+          <t>1728830</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,71%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>103171</t>
+          <t>105371</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>147869</t>
+          <t>147362</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64885</t>
+          <t>63489</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>97038</t>
+          <t>98845</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>176461</t>
+          <t>177311</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>232486</t>
+          <t>231428</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24646</t>
+          <t>24578</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49118</t>
+          <t>49357</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25563</t>
+          <t>25648</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48135</t>
+          <t>49064</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>54971</t>
+          <t>56723</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>88422</t>
+          <t>88578</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>529910</t>
+          <t>531279</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>564015</t>
+          <t>564116</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>608573</t>
+          <t>607807</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>647156</t>
+          <t>647060</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1150093</t>
+          <t>1152390</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1201628</t>
+          <t>1201622</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>46688</t>
+          <t>46480</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>79251</t>
+          <t>77579</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>63729</t>
+          <t>63019</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>96399</t>
+          <t>97505</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>118360</t>
+          <t>117187</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>163398</t>
+          <t>163790</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4352</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17549</t>
+          <t>18486</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18210</t>
+          <t>19437</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40812</t>
+          <t>41819</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26598</t>
+          <t>26436</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52222</t>
+          <t>51725</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>245508</t>
+          <t>245598</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>266456</t>
+          <t>267096</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>898430</t>
+          <t>900106</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>947239</t>
+          <t>948756</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1151971</t>
+          <t>1153958</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1206197</t>
+          <t>1208447</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,63%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15854</t>
+          <t>15314</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>34861</t>
+          <t>34714</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>111272</t>
+          <t>110314</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>155728</t>
+          <t>156879</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>132183</t>
+          <t>131879</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>181300</t>
+          <t>184475</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11524</t>
+          <t>11161</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13036</t>
+          <t>12912</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>32614</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15695</t>
+          <t>16892</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38283</t>
+          <t>38440</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2920993</t>
+          <t>2922638</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2997928</t>
+          <t>2997514</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2987057</t>
+          <t>2993796</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3071510</t>
+          <t>3072020</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5938866</t>
+          <t>5927146</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6055026</t>
+          <t>6047993</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>304222</t>
+          <t>298476</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>371007</t>
+          <t>371832</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>339878</t>
+          <t>342059</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>420028</t>
+          <t>414097</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>658495</t>
+          <t>667895</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>762835</t>
+          <t>772763</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>61569</t>
+          <t>62008</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>97969</t>
+          <t>99843</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>85606</t>
+          <t>86727</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>124738</t>
+          <t>128193</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>160020</t>
+          <t>158663</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>214139</t>
+          <t>212980</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2023</t>
+          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>436326</t>
+          <t>437400</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>467446</t>
+          <t>468506</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>397355</t>
+          <t>398471</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>417402</t>
+          <t>417441</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>843217</t>
+          <t>843276</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>879351</t>
+          <t>880225</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28764</t>
+          <t>29135</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57644</t>
+          <t>56906</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19724</t>
+          <t>19717</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37144</t>
+          <t>35564</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53325</t>
+          <t>53160</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86287</t>
+          <t>86471</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21941</t>
+          <t>19204</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16699</t>
+          <t>17273</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13087</t>
+          <t>13094</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30876</t>
+          <t>31288</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415635</t>
+          <t>415281</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>435835</t>
+          <t>434814</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>332267</t>
+          <t>330906</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>352148</t>
+          <t>352616</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>753637</t>
+          <t>754427</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>782880</t>
+          <t>782952</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,84%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13672</t>
+          <t>14138</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31963</t>
+          <t>33726</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24774</t>
+          <t>24426</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44449</t>
+          <t>44731</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>42425</t>
+          <t>42543</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>69823</t>
+          <t>69629</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,82 +11708,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>6166</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3091</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11489</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>9987</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>5959</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>17269</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>2,07%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6166</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2960</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11688</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>9987</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>5685</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>17328</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>585162</t>
+          <t>585159</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>649881</t>
+          <t>649817</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>137824</t>
+          <t>138034</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>153824</t>
+          <t>154047</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>730747</t>
+          <t>733622</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>804070</t>
+          <t>810225</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13286</t>
+          <t>12268</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64233</t>
+          <t>65089</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10252</t>
+          <t>10158</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25811</t>
+          <t>25930</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22745</t>
+          <t>19997</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82618</t>
+          <t>80260</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>2546</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22865</t>
+          <t>21942</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6701</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4912</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25425</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>940853</t>
+          <t>937980</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>973177</t>
+          <t>973407</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>866739</t>
+          <t>867486</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>935568</t>
+          <t>932246</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1821991</t>
+          <t>1824958</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1899800</t>
+          <t>1897885</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44854</t>
+          <t>46542</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74224</t>
+          <t>77267</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29643</t>
+          <t>31142</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84343</t>
+          <t>84138</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>85013</t>
+          <t>84031</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>148829</t>
+          <t>146243</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10650</t>
+          <t>10060</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27712</t>
+          <t>26952</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9528</t>
+          <t>10763</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31758</t>
+          <t>31882</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25545</t>
+          <t>25166</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>52449</t>
+          <t>50888</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>412257</t>
+          <t>412543</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>437835</t>
+          <t>438669</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>737346</t>
+          <t>736705</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>778060</t>
+          <t>776998</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1158861</t>
+          <t>1160281</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1205272</t>
+          <t>1207951</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23778</t>
+          <t>23383</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>47353</t>
+          <t>46965</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48204</t>
+          <t>47469</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>82021</t>
+          <t>82046</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>82179</t>
+          <t>78936</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>120218</t>
+          <t>117833</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24523</t>
+          <t>24374</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11941</t>
+          <t>11662</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26135</t>
+          <t>26753</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23978</t>
+          <t>23582</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46168</t>
+          <t>47590</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>193289</t>
+          <t>192184</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>226995</t>
+          <t>226658</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>678839</t>
+          <t>679894</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>715337</t>
+          <t>715541</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>891281</t>
+          <t>889113</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>935313</t>
+          <t>934985</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35919</t>
+          <t>37985</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35063</t>
+          <t>33534</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67230</t>
+          <t>64690</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,47 +13454,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
+          <t>8,51%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>63748</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>46361</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>88481</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>6,37%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>4,63%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>8,85%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>63748</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>47803</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>86129</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24164</t>
+          <t>24515</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22896</t>
+          <t>23689</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11624</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>35953</t>
+          <t>38608</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3053956</t>
+          <t>3053459</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3158715</t>
+          <t>3157707</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3212516</t>
+          <t>3210513</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3310019</t>
+          <t>3308420</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6284620</t>
+          <t>6289112</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6424311</t>
+          <t>6433257</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,61%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>162016</t>
+          <t>162099</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>247985</t>
+          <t>246505</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>204105</t>
+          <t>205614</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>284751</t>
+          <t>285412</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>398848</t>
+          <t>397306</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>514799</t>
+          <t>511616</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>46836</t>
+          <t>48167</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>87666</t>
+          <t>86393</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>55178</t>
+          <t>56223</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>88174</t>
+          <t>90705</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>111938</t>
+          <t>111003</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>163324</t>
+          <t>162800</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A02-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P05A02-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>363388</t>
+          <t>359264</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>398607</t>
+          <t>395942</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>215258</t>
+          <t>217403</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>246642</t>
+          <t>246154</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>587487</t>
+          <t>588891</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>636156</t>
+          <t>635025</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,54%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66427</t>
+          <t>67830</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100484</t>
+          <t>102573</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44759</t>
+          <t>43729</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72213</t>
+          <t>72390</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117260</t>
+          <t>119738</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>162623</t>
+          <t>165474</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17409</t>
+          <t>16153</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>10704</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26311</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17019</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36747</t>
+          <t>37808</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>264225</t>
+          <t>264077</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>296787</t>
+          <t>295780</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>274948</t>
+          <t>274170</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>304375</t>
+          <t>305417</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>548855</t>
+          <t>546578</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>593202</t>
+          <t>592451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,6%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56950</t>
+          <t>56808</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>86467</t>
+          <t>86303</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49999</t>
+          <t>48900</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>79175</t>
+          <t>78285</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>113492</t>
+          <t>114026</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>159289</t>
+          <t>157115</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7348</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21853</t>
+          <t>22494</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>8862</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27083</t>
+          <t>25051</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20758</t>
+          <t>20362</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44263</t>
+          <t>41667</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>403841</t>
+          <t>405726</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>445273</t>
+          <t>444329</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>111235</t>
+          <t>110974</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>133356</t>
+          <t>133404</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>526194</t>
+          <t>526052</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>571118</t>
+          <t>572075</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,66%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77336</t>
+          <t>76829</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>113345</t>
+          <t>111563</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25407</t>
+          <t>25718</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45671</t>
+          <t>46522</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107784</t>
+          <t>109341</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>150312</t>
+          <t>150968</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13360</t>
+          <t>13775</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32522</t>
+          <t>33692</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16468</t>
+          <t>16879</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20851</t>
+          <t>21459</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44496</t>
+          <t>43097</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>907884</t>
+          <t>907302</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>965469</t>
+          <t>968755</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>505094</t>
+          <t>505470</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>552601</t>
+          <t>552930</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1430033</t>
+          <t>1429893</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1505107</t>
+          <t>1506917</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,32%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>236433</t>
+          <t>236259</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>292540</t>
+          <t>293166</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>127942</t>
+          <t>125087</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>170742</t>
+          <t>168913</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>376243</t>
+          <t>376421</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>447395</t>
+          <t>449764</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24984</t>
+          <t>24293</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48507</t>
+          <t>49985</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24261</t>
+          <t>24641</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47493</t>
+          <t>48221</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>55927</t>
+          <t>54238</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>88742</t>
+          <t>86244</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257938</t>
+          <t>257667</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>288919</t>
+          <t>288519</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>390259</t>
+          <t>392559</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>433438</t>
+          <t>433973</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>659426</t>
+          <t>659299</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>714111</t>
+          <t>713350</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,85%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52989</t>
+          <t>53865</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>83338</t>
+          <t>82888</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>106991</t>
+          <t>106781</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>146716</t>
+          <t>145734</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>169367</t>
+          <t>167867</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>218669</t>
+          <t>218290</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4337</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15423</t>
+          <t>14381</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20351</t>
+          <t>20289</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43240</t>
+          <t>43212</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25831</t>
+          <t>26363</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50439</t>
+          <t>52247</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>243360</t>
+          <t>242440</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>266362</t>
+          <t>265333</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>884908</t>
+          <t>890618</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>948105</t>
+          <t>951744</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1139118</t>
+          <t>1142074</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1207076</t>
+          <t>1205737</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,03%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24466</t>
+          <t>25557</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45327</t>
+          <t>45805</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>223888</t>
+          <t>219504</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>278956</t>
+          <t>275883</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>252013</t>
+          <t>254962</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>313385</t>
+          <t>312242</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15356</t>
+          <t>14927</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>63606</t>
+          <t>65284</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>98793</t>
+          <t>99618</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>71047</t>
+          <t>70373</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>109821</t>
+          <t>107744</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2509524</t>
+          <t>2509947</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2600413</t>
+          <t>2604318</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2455804</t>
+          <t>2451894</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2561670</t>
+          <t>2555971</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4996130</t>
+          <t>4990492</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5132656</t>
+          <t>5129711</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,33%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>568943</t>
+          <t>565983</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>654484</t>
+          <t>657140</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>627226</t>
+          <t>631769</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>722642</t>
+          <t>727714</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1224610</t>
+          <t>1224604</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1355178</t>
+          <t>1354811</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>76806</t>
+          <t>78265</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>115607</t>
+          <t>116922</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>160339</t>
+          <t>161476</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>215160</t>
+          <t>216216</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>250513</t>
+          <t>253604</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>313737</t>
+          <t>317368</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>358181</t>
+          <t>359246</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>388201</t>
+          <t>388932</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>246347</t>
+          <t>243362</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>273642</t>
+          <t>272529</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>609304</t>
+          <t>609569</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>653875</t>
+          <t>653581</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,18%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33175</t>
+          <t>34390</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60052</t>
+          <t>60211</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30680</t>
+          <t>31605</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57130</t>
+          <t>59395</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72457</t>
+          <t>70832</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>111106</t>
+          <t>111053</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>10649</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26039</t>
+          <t>27000</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17090</t>
+          <t>16492</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17431</t>
+          <t>17705</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38038</t>
+          <t>37733</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>323371</t>
+          <t>324729</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>359100</t>
+          <t>358792</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>266191</t>
+          <t>268533</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>295756</t>
+          <t>295889</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>602307</t>
+          <t>602504</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>645996</t>
+          <t>647895</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,25%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50739</t>
+          <t>50683</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83775</t>
+          <t>84024</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31204</t>
+          <t>30440</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59491</t>
+          <t>56008</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>89303</t>
+          <t>87832</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>133447</t>
+          <t>130097</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15972</t>
+          <t>16114</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3493</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16229</t>
+          <t>17691</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9661</t>
+          <t>9171</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27422</t>
+          <t>25881</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>519418</t>
+          <t>518437</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>554320</t>
+          <t>553732</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>206520</t>
+          <t>206602</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>230281</t>
+          <t>230257</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>732007</t>
+          <t>734674</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>775117</t>
+          <t>776776</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,57%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60048</t>
+          <t>60112</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93940</t>
+          <t>94869</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21545</t>
+          <t>21104</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43405</t>
+          <t>42654</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88382</t>
+          <t>88777</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131320</t>
+          <t>128928</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8902</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24516</t>
+          <t>23400</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>4582</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15991</t>
+          <t>15746</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15463</t>
+          <t>15732</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35963</t>
+          <t>35333</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>950681</t>
+          <t>951986</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1001012</t>
+          <t>1002842</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>599376</t>
+          <t>603476</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>646174</t>
+          <t>647609</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1569005</t>
+          <t>1566629</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1635672</t>
+          <t>1635860</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,35%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>114922</t>
+          <t>113806</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>161977</t>
+          <t>160127</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87697</t>
+          <t>87034</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129096</t>
+          <t>128352</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>215264</t>
+          <t>213961</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>275545</t>
+          <t>276460</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25494</t>
+          <t>24046</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50145</t>
+          <t>50293</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21737</t>
+          <t>22821</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47504</t>
+          <t>46624</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>54354</t>
+          <t>53014</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>88923</t>
+          <t>87922</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>414011</t>
+          <t>415143</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>448543</t>
+          <t>447431</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>611999</t>
+          <t>614060</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>653607</t>
+          <t>653025</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1036532</t>
+          <t>1040313</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1092923</t>
+          <t>1092601</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,95%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>55604</t>
+          <t>56067</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>88592</t>
+          <t>86827</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>80508</t>
+          <t>81336</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>115610</t>
+          <t>115081</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>144610</t>
+          <t>144316</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>198332</t>
+          <t>191685</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16120</t>
+          <t>15843</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19056</t>
+          <t>18493</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41772</t>
+          <t>40978</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25746</t>
+          <t>25406</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52083</t>
+          <t>50768</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>214394</t>
+          <t>213827</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>238087</t>
+          <t>238591</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>899633</t>
+          <t>899709</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>949390</t>
+          <t>947010</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1124789</t>
+          <t>1123688</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1179843</t>
+          <t>1179276</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,82%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27639</t>
+          <t>26367</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50578</t>
+          <t>50540</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>125736</t>
+          <t>126485</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>169186</t>
+          <t>171307</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>160675</t>
+          <t>159154</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>210639</t>
+          <t>212082</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6219</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>23880</t>
+          <t>25518</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>49060</t>
+          <t>50476</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>25932</t>
+          <t>25964</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>51881</t>
+          <t>51293</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2852244</t>
+          <t>2847267</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2939819</t>
+          <t>2933359</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2897978</t>
+          <t>2899179</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2992114</t>
+          <t>2993003</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5776324</t>
+          <t>5767819</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5902151</t>
+          <t>5896977</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,85%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>388932</t>
+          <t>392117</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>473432</t>
+          <t>476411</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>427725</t>
+          <t>423835</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>513465</t>
+          <t>508363</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>845136</t>
+          <t>845267</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>960511</t>
+          <t>968205</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>67767</t>
+          <t>68613</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>105566</t>
+          <t>106066</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>100941</t>
+          <t>102561</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>146910</t>
+          <t>147041</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>182241</t>
+          <t>179658</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>240191</t>
+          <t>238254</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>362739</t>
+          <t>363307</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>390306</t>
+          <t>391285</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>278947</t>
+          <t>278033</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>305255</t>
+          <t>306043</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>652000</t>
+          <t>651270</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>688027</t>
+          <t>689760</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,23%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31276</t>
+          <t>31516</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57389</t>
+          <t>58338</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28141</t>
+          <t>27534</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51502</t>
+          <t>51965</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65490</t>
+          <t>65218</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99170</t>
+          <t>99500</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14331</t>
+          <t>14197</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7114</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21988</t>
+          <t>22381</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12374</t>
+          <t>11599</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31373</t>
+          <t>30076</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>317799</t>
+          <t>317427</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>342553</t>
+          <t>342093</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>310244</t>
+          <t>308654</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>335500</t>
+          <t>335155</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>637520</t>
+          <t>632297</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>672491</t>
+          <t>670448</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,4%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24021</t>
+          <t>23964</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46829</t>
+          <t>47098</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27663</t>
+          <t>28612</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>52492</t>
+          <t>53117</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>57185</t>
+          <t>59485</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>90701</t>
+          <t>92553</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16497</t>
+          <t>16664</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11841</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>7353</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22073</t>
+          <t>23464</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>440267</t>
+          <t>441220</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>470455</t>
+          <t>470846</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>145563</t>
+          <t>146461</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>159384</t>
+          <t>159606</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>591645</t>
+          <t>592315</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>625931</t>
+          <t>626531</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,06%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37594</t>
+          <t>37197</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63779</t>
+          <t>64146</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18218</t>
+          <t>17419</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46106</t>
+          <t>45502</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76388</t>
+          <t>76132</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9043</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25660</t>
+          <t>26136</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10730</t>
+          <t>10801</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27377</t>
+          <t>27247</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>960946</t>
+          <t>963687</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1010416</t>
+          <t>1011019</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>687227</t>
+          <t>688587</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>726639</t>
+          <t>727923</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1662571</t>
+          <t>1663755</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1728830</t>
+          <t>1726150</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,57%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105371</t>
+          <t>103448</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>147362</t>
+          <t>145866</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>63489</t>
+          <t>63327</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>98845</t>
+          <t>96479</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>177311</t>
+          <t>179939</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>231428</t>
+          <t>234390</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24578</t>
+          <t>25184</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49357</t>
+          <t>49415</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25648</t>
+          <t>24831</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49064</t>
+          <t>48058</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>56723</t>
+          <t>55486</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>88578</t>
+          <t>90232</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>531279</t>
+          <t>530282</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>564116</t>
+          <t>562559</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>607807</t>
+          <t>607731</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>647060</t>
+          <t>647822</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1152390</t>
+          <t>1150350</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1201622</t>
+          <t>1202005</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,71%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>46480</t>
+          <t>47871</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>77579</t>
+          <t>78044</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>63019</t>
+          <t>63344</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>97505</t>
+          <t>96959</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>117187</t>
+          <t>117853</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>163790</t>
+          <t>164573</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4352</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18486</t>
+          <t>20031</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19437</t>
+          <t>18626</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41819</t>
+          <t>41425</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26436</t>
+          <t>26906</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51725</t>
+          <t>51071</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>245598</t>
+          <t>245416</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>267096</t>
+          <t>266832</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>900106</t>
+          <t>900168</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>948756</t>
+          <t>948654</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1153958</t>
+          <t>1156216</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1208447</t>
+          <t>1208710</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,65%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15314</t>
+          <t>15350</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>34714</t>
+          <t>34876</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>110314</t>
+          <t>110271</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>156879</t>
+          <t>154779</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>131879</t>
+          <t>132551</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>184475</t>
+          <t>181328</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11161</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12912</t>
+          <t>12828</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>32614</t>
+          <t>31316</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16892</t>
+          <t>16236</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38440</t>
+          <t>37149</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2922638</t>
+          <t>2919470</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2997514</t>
+          <t>2998180</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2993796</t>
+          <t>2992384</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3072020</t>
+          <t>3076041</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5927146</t>
+          <t>5937638</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6047993</t>
+          <t>6048985</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,77%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>298476</t>
+          <t>304557</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>371832</t>
+          <t>373406</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>342059</t>
+          <t>339593</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>414097</t>
+          <t>415184</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>667895</t>
+          <t>664659</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>772763</t>
+          <t>766915</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>62008</t>
+          <t>62831</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>99843</t>
+          <t>99393</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>86727</t>
+          <t>87399</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>128193</t>
+          <t>129237</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>158663</t>
+          <t>160739</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>212980</t>
+          <t>214297</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -11006,32 +11006,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>454693</t>
+          <t>494378</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>437400</t>
+          <t>476093</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>468506</t>
+          <t>508034</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11041,32 +11041,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>408343</t>
+          <t>442791</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>398471</t>
+          <t>428982</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>417441</t>
+          <t>451989</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11076,32 +11076,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>863036</t>
+          <t>937169</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>843276</t>
+          <t>913996</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>880225</t>
+          <t>953940</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>91,94%</t>
         </is>
       </c>
     </row>
@@ -11119,32 +11119,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>40598</t>
+          <t>45627</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29135</t>
+          <t>33939</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56906</t>
+          <t>63038</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11154,32 +11154,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27467</t>
+          <t>32830</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19717</t>
+          <t>24533</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35564</t>
+          <t>44017</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,32 +11189,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>68065</t>
+          <t>78457</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53160</t>
+          <t>64172</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86471</t>
+          <t>99860</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -11232,32 +11232,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9922</t>
+          <t>10613</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19204</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11267,32 +11267,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>11358</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5944</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17273</t>
+          <t>17760</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11302,32 +11302,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>20236</t>
+          <t>21971</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13094</t>
+          <t>13884</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31288</t>
+          <t>33421</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>446125</t>
+          <t>486979</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>446125</t>
+          <t>486979</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>446125</t>
+          <t>486979</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>951337</t>
+          <t>1037597</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>951337</t>
+          <t>1037597</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>951337</t>
+          <t>1037597</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11462,32 +11462,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>426687</t>
+          <t>456756</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415281</t>
+          <t>444822</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>434814</t>
+          <t>465884</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11497,32 +11497,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>343308</t>
+          <t>379618</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>330906</t>
+          <t>368221</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>352616</t>
+          <t>388397</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,32 +11532,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>769994</t>
+          <t>836373</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>754427</t>
+          <t>819567</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>782952</t>
+          <t>851040</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -11575,32 +11575,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21705</t>
+          <t>22542</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14138</t>
+          <t>14499</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33726</t>
+          <t>33514</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11610,32 +11610,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32671</t>
+          <t>35887</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24426</t>
+          <t>27817</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44731</t>
+          <t>47045</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,32 +11645,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>54376</t>
+          <t>58429</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>42543</t>
+          <t>45047</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>69629</t>
+          <t>73901</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -11688,32 +11688,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>10289</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6166</t>
+          <t>7182</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3091</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11489</t>
+          <t>13235</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>11097</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>6080</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17269</t>
+          <t>18401</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>382144</t>
+          <t>422687</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>382144</t>
+          <t>422687</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>382144</t>
+          <t>422687</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>834357</t>
+          <t>905899</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>834357</t>
+          <t>905899</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>834357</t>
+          <t>905899</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,32 +11918,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>619489</t>
+          <t>416531</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>585159</t>
+          <t>399629</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>649817</t>
+          <t>430941</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11953,67 +11953,67 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>147342</t>
+          <t>164255</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>138034</t>
+          <t>153613</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>154047</t>
+          <t>171530</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
+          <t>87,6%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>81,93%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>91,48%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>580786</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>560522</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>596131</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
           <t>88,28%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>82,7%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>92,29%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>766831</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>733622</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>810225</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>91,94%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>90,61%</t>
         </is>
       </c>
     </row>
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36787</t>
+          <t>42419</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12268</t>
+          <t>30911</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65089</t>
+          <t>57626</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16308</t>
+          <t>19727</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10158</t>
+          <t>12521</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25930</t>
+          <t>30392</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>53095</t>
+          <t>62146</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19997</t>
+          <t>47939</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80260</t>
+          <t>80797</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10878</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2546</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21942</t>
+          <t>22671</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>6982</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>14139</t>
+          <t>14991</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>8396</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25425</t>
+          <t>25227</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>667153</t>
+          <t>470426</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>667153</t>
+          <t>470426</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>667153</t>
+          <t>470426</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>834064</t>
+          <t>657923</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>834064</t>
+          <t>657923</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>834064</t>
+          <t>657923</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,32 +12374,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>957410</t>
+          <t>1043505</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>937980</t>
+          <t>1023326</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>973407</t>
+          <t>1061037</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>896266</t>
+          <t>769610</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>867486</t>
+          <t>750691</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>932246</t>
+          <t>784216</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1853676</t>
+          <t>1813116</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1824958</t>
+          <t>1787162</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1897885</t>
+          <t>1836910</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>92,27%</t>
         </is>
       </c>
     </row>
@@ -12487,32 +12487,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>58983</t>
+          <t>66380</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46542</t>
+          <t>50767</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>77267</t>
+          <t>83774</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>61082</t>
+          <t>66896</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31142</t>
+          <t>54284</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84138</t>
+          <t>84184</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>120065</t>
+          <t>133276</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>84031</t>
+          <t>112899</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>146243</t>
+          <t>154950</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -12600,32 +12600,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17242</t>
+          <t>19754</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10060</t>
+          <t>12290</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26952</t>
+          <t>29857</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20746</t>
+          <t>24705</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10763</t>
+          <t>17496</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31882</t>
+          <t>34457</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>37988</t>
+          <t>44459</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25166</t>
+          <t>33447</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>50888</t>
+          <t>58496</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1033635</t>
+          <t>1129639</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1033635</t>
+          <t>1129639</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1033635</t>
+          <t>1129639</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2011729</t>
+          <t>1990851</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2011729</t>
+          <t>1990851</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2011729</t>
+          <t>1990851</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,32 +12830,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>425635</t>
+          <t>510398</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>412543</t>
+          <t>493832</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>438669</t>
+          <t>523475</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>755267</t>
+          <t>727972</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>736705</t>
+          <t>711842</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>776998</t>
+          <t>743781</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,32 +12900,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1180901</t>
+          <t>1238371</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1160281</t>
+          <t>1216617</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1207951</t>
+          <t>1258991</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>90,09%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>33902</t>
+          <t>40618</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23383</t>
+          <t>29384</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>46965</t>
+          <t>53695</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>66668</t>
+          <t>81540</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>47469</t>
+          <t>67824</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>82046</t>
+          <t>96491</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>100569</t>
+          <t>122158</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>78936</t>
+          <t>103881</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>117833</t>
+          <t>141362</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -13056,102 +13056,102 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>15509</t>
+          <t>16948</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>10661</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24374</t>
+          <t>28332</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4,99%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>19972</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>13114</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>27947</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>36920</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>27368</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>49331</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>1,96%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>18198</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>11662</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>26753</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>33707</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>23582</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>47590</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>840133</t>
+          <t>829484</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>840133</t>
+          <t>829484</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>840133</t>
+          <t>829484</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1315178</t>
+          <t>1397448</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1315178</t>
+          <t>1397448</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1315178</t>
+          <t>1397448</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13286,32 +13286,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>214021</t>
+          <t>212136</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>192184</t>
+          <t>194330</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>226658</t>
+          <t>224707</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>701682</t>
+          <t>776833</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>679894</t>
+          <t>757768</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>715541</t>
+          <t>792576</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>915703</t>
+          <t>988968</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>889113</t>
+          <t>963379</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>934985</t>
+          <t>1007963</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -13399,32 +13399,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>17870</t>
+          <t>17694</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>8092</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37985</t>
+          <t>35432</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>45877</t>
+          <t>54432</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33534</t>
+          <t>40223</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>64690</t>
+          <t>72401</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>63748</t>
+          <t>72126</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>46361</t>
+          <t>54683</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>88481</t>
+          <t>94740</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -13512,32 +13512,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>8615</t>
+          <t>7398</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24515</t>
+          <t>19490</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13547,32 +13547,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>12246</t>
+          <t>12585</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23689</t>
+          <t>21635</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>20861</t>
+          <t>19982</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12103</t>
+          <t>11704</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38608</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>759805</t>
+          <t>843849</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>759805</t>
+          <t>843849</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>759805</t>
+          <t>843849</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1000312</t>
+          <t>1081076</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1000312</t>
+          <t>1081076</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1000312</t>
+          <t>1081076</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3097934</t>
+          <t>3133703</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3053459</t>
+          <t>3097343</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3157707</t>
+          <t>3168976</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3252206</t>
+          <t>3261079</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3210513</t>
+          <t>3227541</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3308420</t>
+          <t>3294628</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>6350141</t>
+          <t>6394783</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6289112</t>
+          <t>6343603</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6433257</t>
+          <t>6441364</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>91,1%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>209845</t>
+          <t>235280</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>162099</t>
+          <t>205099</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>246505</t>
+          <t>270165</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>250073</t>
+          <t>291312</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>205614</t>
+          <t>260398</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>285412</t>
+          <t>323492</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>459918</t>
+          <t>526592</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>397306</t>
+          <t>483732</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>511616</t>
+          <t>569686</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>65987</t>
+          <t>70103</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>48167</t>
+          <t>53924</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>86393</t>
+          <t>90775</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>70931</t>
+          <t>79316</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>56223</t>
+          <t>64832</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>90705</t>
+          <t>96020</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>136918</t>
+          <t>149419</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>111003</t>
+          <t>128288</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>162800</t>
+          <t>176163</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3373766</t>
+          <t>3439086</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3373766</t>
+          <t>3439086</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3373766</t>
+          <t>3439086</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3573210</t>
+          <t>3631708</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3573210</t>
+          <t>3631708</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3573210</t>
+          <t>3631708</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6946977</t>
+          <t>7070794</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6946977</t>
+          <t>7070794</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6946977</t>
+          <t>7070794</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
